--- a/artfynd/A 8753-2022 artfynd.xlsx
+++ b/artfynd/A 8753-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 8753-2022 artfynd.xlsx
+++ b/artfynd/A 8753-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1465,6 +1465,103 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131619498</v>
+      </c>
+      <c r="B8" t="n">
+        <v>75366</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lushagen 8,5 km VSV om Forsmarks kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>666590</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6693338</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8753-2022 artfynd.xlsx
+++ b/artfynd/A 8753-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1465,103 +1465,6 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>131619498</v>
-      </c>
-      <c r="B8" t="n">
-        <v>75366</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>6426</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Kattfotslav</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Felipes leucopellaeus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Lushagen 8,5 km VSV om Forsmarks kyrka, Upl</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>666590</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6693338</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Östhammar</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Forsmark</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8753-2022 artfynd.xlsx
+++ b/artfynd/A 8753-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>60780693</v>
+        <v>60899639</v>
       </c>
       <c r="B2" t="n">
-        <v>90656</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87195</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6003297</v>
+        <v>426</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spricktaggsvamp</t>
+          <t>Gyllenspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum glaucopus</t>
+          <t>Cortinarius aureofulvus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>666576.8810962436</v>
+        <v>666679</v>
       </c>
       <c r="R2" t="n">
-        <v>6693312.018818907</v>
+        <v>6693341</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,24 +752,14 @@
           <t>2006-09-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2006-09-29</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1 ex. i barrmatta under gran, i äldre granskog.</t>
+          <t>1 ex. under tall i äldre barrskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,15 +773,9 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Äldre, örtrik granskog.</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>Uppsala-Evolutionsmuseet</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr"/>
+          <t>Äldre, örtrik barrskog.</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -812,42 +791,33 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>60899639</v>
+        <v>75882352</v>
       </c>
       <c r="B3" t="n">
-        <v>85128</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87412</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>426</v>
+        <v>3624</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gyllenspindling</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius aureofulvus</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>M. M. Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -861,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>666678.8167382773</v>
+        <v>666600</v>
       </c>
       <c r="R3" t="n">
-        <v>6693341.47854041</v>
+        <v>6693206</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,24 +864,14 @@
           <t>2006-09-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2006-09-29</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1 ex. under tall i äldre barrskog.</t>
+          <t>Ca. 20 ex. i äldre barrskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -946,12 +906,7 @@
         <v>69510565</v>
       </c>
       <c r="B4" t="n">
-        <v>85077</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>666584.7124634802</v>
+        <v>666585</v>
       </c>
       <c r="R4" t="n">
-        <v>6693336.173607421</v>
+        <v>6693336</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1025,19 +980,9 @@
           <t>2006-09-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2006-09-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1077,16 +1022,11 @@
         <v>69524749</v>
       </c>
       <c r="B5" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1123,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>666732.5265873537</v>
+        <v>666733</v>
       </c>
       <c r="R5" t="n">
-        <v>6693372.199059295</v>
+        <v>6693372</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1156,19 +1096,9 @@
           <t>2006-09-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2006-09-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1208,16 +1138,11 @@
         <v>69524750</v>
       </c>
       <c r="B6" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1254,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>666629.118247909</v>
+        <v>666629</v>
       </c>
       <c r="R6" t="n">
-        <v>6693374.893849079</v>
+        <v>6693375</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1287,19 +1212,9 @@
           <t>2006-09-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2006-09-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1339,12 +1254,7 @@
         <v>75905836</v>
       </c>
       <c r="B7" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1366,7 +1276,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1385,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>666619.6646545628</v>
+        <v>666620</v>
       </c>
       <c r="R7" t="n">
-        <v>6693353.639299922</v>
+        <v>6693354</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1418,19 +1328,9 @@
           <t>2006-09-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2006-09-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1464,6 +1364,128 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>60780693</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93200</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6003297</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spricktaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum glaucopus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lushagen 8,5 km VSV om Forsmarks kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>666577</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6693312</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2006-09-29</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2006-09-29</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1 ex. i barrmatta under gran, i äldre granskog.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Äldre, örtrik granskog.</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>Uppsala-Evolutionsmuseet</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
